--- a/outputs/performance_report.xlsx
+++ b/outputs/performance_report.xlsx
@@ -474,31 +474,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
-        <v>0.46</v>
+        <v>0.464</v>
       </c>
       <c r="E2" t="n">
-        <v>1425.69</v>
+        <v>1444.86</v>
       </c>
       <c r="F2" t="n">
-        <v>-57.55</v>
+        <v>-49.92</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0404</v>
+        <v>-0.0346</v>
       </c>
       <c r="H2" t="n">
-        <v>0.543</v>
+        <v>0.542</v>
       </c>
       <c r="I2" t="n">
         <v>-0.0009</v>
       </c>
       <c r="J2" t="n">
-        <v>0.47</v>
+        <v>0.455</v>
       </c>
     </row>
   </sheetData>
@@ -574,31 +574,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.588</v>
       </c>
       <c r="E2" t="n">
-        <v>211</v>
+        <v>223.12</v>
       </c>
       <c r="F2" t="n">
-        <v>7.85</v>
+        <v>20.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0372</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>0.51</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0033</v>
+        <v>0.0059</v>
       </c>
       <c r="J2" t="n">
-        <v>0.571</v>
+        <v>0.588</v>
       </c>
     </row>
     <row r="3">
@@ -642,31 +642,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.422</v>
+        <v>0.42</v>
       </c>
       <c r="E4" t="n">
-        <v>660.23</v>
+        <v>664.1900000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>-68.41</v>
+        <v>-70.55</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1036</v>
+        <v>-0.1062</v>
       </c>
       <c r="H4" t="n">
-        <v>0.553</v>
+        <v>0.551</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0061</v>
+        <v>-0.0067</v>
       </c>
       <c r="J4" t="n">
-        <v>0.378</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="5">
@@ -676,31 +676,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>0.571</v>
+        <v>0.545</v>
       </c>
       <c r="E5" t="n">
-        <v>315.21</v>
+        <v>317.62</v>
       </c>
       <c r="F5" t="n">
-        <v>14.74</v>
+        <v>12.33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0468</v>
+        <v>0.0388</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.008</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.333</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="6">
@@ -710,31 +710,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>0.357</v>
+        <v>0.333</v>
       </c>
       <c r="E6" t="n">
-        <v>154.12</v>
+        <v>154.8</v>
       </c>
       <c r="F6" t="n">
-        <v>-26.54</v>
+        <v>-27.22</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1722</v>
+        <v>-0.1758</v>
       </c>
       <c r="H6" t="n">
-        <v>0.527</v>
+        <v>0.528</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0127</v>
+        <v>0.0123</v>
       </c>
       <c r="J6" t="n">
-        <v>0.786</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>
@@ -810,31 +810,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>0.455</v>
+        <v>0.444</v>
       </c>
       <c r="E2" t="n">
-        <v>941.6</v>
+        <v>947.97</v>
       </c>
       <c r="F2" t="n">
-        <v>-48.96</v>
+        <v>-53.5</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.052</v>
+        <v>-0.0564</v>
       </c>
       <c r="H2" t="n">
         <v>0.539</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0062</v>
+        <v>-0.0068</v>
       </c>
       <c r="J2" t="n">
-        <v>0.379</v>
+        <v>0.347</v>
       </c>
     </row>
     <row r="3">
@@ -844,31 +844,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>0.471</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>484.09</v>
+        <v>496.89</v>
       </c>
       <c r="F3" t="n">
-        <v>-8.59</v>
+        <v>3.58</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0177</v>
+        <v>0.0072</v>
       </c>
       <c r="H3" t="n">
-        <v>0.552</v>
+        <v>0.548</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0092</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.647</v>
+        <v>0.658</v>
       </c>
     </row>
   </sheetData>
@@ -919,16 +919,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>0.479</v>
+        <v>0.482</v>
       </c>
       <c r="D2" t="n">
-        <v>0.35</v>
+        <v>0.375</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.129</v>
+        <v>-0.107</v>
       </c>
     </row>
     <row r="3">
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
         <v>0.537</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.025</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="4">
@@ -957,16 +957,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C4" t="n">
         <v>0.5610000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.455</v>
+        <v>0.472</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.106</v>
+        <v>-0.089</v>
       </c>
     </row>
     <row r="5">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>0.594</v>
+        <v>0.593</v>
       </c>
       <c r="D5" t="n">
-        <v>0.308</v>
+        <v>0.286</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.286</v>
+        <v>-0.307</v>
       </c>
     </row>
     <row r="6">
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD101"/>
+  <dimension ref="A1:AF111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1191,6 +1191,16 @@
           <t>inj_note</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>abs_spread</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1309,6 +1319,8 @@
           <t xml:space="preserve">Jusuf Nurkic out; Tony Bradley out; Trey Alexander out; </t>
         </is>
       </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1427,6 +1439,8 @@
           <t xml:space="preserve">Jusuf Nurkic out; Tony Bradley out; Trey Alexander out; </t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1545,6 +1559,8 @@
           <t xml:space="preserve">Grant Williams out; Coby White out; Kon Knueppel out; </t>
         </is>
       </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1661,6 +1677,8 @@
           <t xml:space="preserve">T.J. McConnell out; Aaron Nesmith out; Johnny Furphy out; </t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1777,6 +1795,8 @@
           <t xml:space="preserve">T.J. McConnell out; Aaron Nesmith out; Johnny Furphy out; </t>
         </is>
       </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1895,6 +1915,8 @@
           <t xml:space="preserve">Grant Williams out; Coby White out; Kon Knueppel out; </t>
         </is>
       </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2011,6 +2033,8 @@
           <t xml:space="preserve">Donte DiVincenzo out; </t>
         </is>
       </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2125,6 +2149,8 @@
         <v>0</v>
       </c>
       <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2237,6 +2263,8 @@
         <v>0</v>
       </c>
       <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2355,6 +2383,8 @@
           <t xml:space="preserve">Grant Williams out; Coby White out; Kon Knueppel out; </t>
         </is>
       </c>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2469,6 +2499,8 @@
         <v>0</v>
       </c>
       <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2581,6 +2613,8 @@
         <v>0</v>
       </c>
       <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2697,6 +2731,8 @@
           <t xml:space="preserve">Branden Carlson out; Shaedon Sharpe out; </t>
         </is>
       </c>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2813,6 +2849,8 @@
           <t xml:space="preserve">Jimmy Butler III out; Kristaps Porzingis out; Moses Moody out; Brandin Podziemski out; </t>
         </is>
       </c>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2931,6 +2969,8 @@
           <t xml:space="preserve">Dylan Cardwell out; Maxime Raynaud out; </t>
         </is>
       </c>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3049,6 +3089,8 @@
           <t xml:space="preserve">Grant Williams out; Coby White out; Kon Knueppel out; </t>
         </is>
       </c>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3167,6 +3209,8 @@
           <t xml:space="preserve">T.J. McConnell out; Aaron Nesmith out; Johnny Furphy out; </t>
         </is>
       </c>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3285,6 +3329,8 @@
           <t xml:space="preserve">Donte DiVincenzo out; </t>
         </is>
       </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3397,6 +3443,8 @@
           <t xml:space="preserve">Grant Williams out; Coby White out; Kon Knueppel out; </t>
         </is>
       </c>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3515,6 +3563,8 @@
           <t xml:space="preserve">Nic Claxton out; Jordan Hawkins out; </t>
         </is>
       </c>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3633,6 +3683,8 @@
           <t xml:space="preserve">Dylan Cardwell out; Maxime Raynaud out; </t>
         </is>
       </c>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3747,6 +3799,8 @@
         <v>0</v>
       </c>
       <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr"/>
+      <c r="AF23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3861,6 +3915,8 @@
         <v>0</v>
       </c>
       <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3975,6 +4031,8 @@
         <v>0</v>
       </c>
       <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4091,6 +4149,8 @@
           <t xml:space="preserve">Grant Williams out; Coby White out; Kon Knueppel out; </t>
         </is>
       </c>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4209,6 +4269,8 @@
           <t xml:space="preserve">T.J. McConnell out; Aaron Nesmith out; Johnny Furphy out; </t>
         </is>
       </c>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4327,6 +4389,8 @@
           <t xml:space="preserve">Mouhamed Gueye out; </t>
         </is>
       </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4443,6 +4507,8 @@
           <t xml:space="preserve">Brandon Ingram out; Max Strus out; Jordan Miller out; Yanic Konan Niederhauser out; </t>
         </is>
       </c>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4557,6 +4623,8 @@
         <v>0</v>
       </c>
       <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4675,6 +4743,8 @@
           <t xml:space="preserve">Jonathan Isaac out; Anthony Black out; Noah Penda out; </t>
         </is>
       </c>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4791,6 +4861,8 @@
           <t xml:space="preserve">T.J. McConnell out; Aaron Nesmith out; Johnny Furphy out; </t>
         </is>
       </c>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4909,6 +4981,8 @@
           <t xml:space="preserve">Brandon Ingram out; Max Strus out; Jordan Miller out; Yanic Konan Niederhauser out; </t>
         </is>
       </c>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5027,6 +5101,8 @@
           <t xml:space="preserve">Caleb Martin out; Santi Aldama out; </t>
         </is>
       </c>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5143,6 +5219,8 @@
           <t xml:space="preserve">Dylan Cardwell out; Maxime Raynaud out; </t>
         </is>
       </c>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5255,6 +5333,8 @@
         <v>0</v>
       </c>
       <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5367,6 +5447,8 @@
           <t xml:space="preserve">Nic Claxton out; Jordan Hawkins out; </t>
         </is>
       </c>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5479,6 +5561,8 @@
         <v>0</v>
       </c>
       <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5597,6 +5681,8 @@
           <t xml:space="preserve">Dylan Cardwell out; Maxime Raynaud out; </t>
         </is>
       </c>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5711,6 +5797,8 @@
         <v>0</v>
       </c>
       <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr"/>
+      <c r="AF40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5829,6 +5917,8 @@
           <t xml:space="preserve">Jimmy Butler III out; Kristaps Porzingis out; Moses Moody out; Brandin Podziemski out; </t>
         </is>
       </c>
+      <c r="AE41" t="inlineStr"/>
+      <c r="AF41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5947,6 +6037,8 @@
           <t xml:space="preserve">Jonathan Isaac out; Anthony Black out; Noah Penda out; </t>
         </is>
       </c>
+      <c r="AE42" t="inlineStr"/>
+      <c r="AF42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6061,6 +6153,8 @@
         <v>0</v>
       </c>
       <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr"/>
+      <c r="AF43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6179,6 +6273,8 @@
           <t xml:space="preserve">Jonathan Isaac out; Anthony Black out; Noah Penda out; </t>
         </is>
       </c>
+      <c r="AE44" t="inlineStr"/>
+      <c r="AF44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6297,6 +6393,8 @@
           <t xml:space="preserve">Brandon Ingram out; Max Strus out; Jordan Miller out; Yanic Konan Niederhauser out; </t>
         </is>
       </c>
+      <c r="AE45" t="inlineStr"/>
+      <c r="AF45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6413,6 +6511,8 @@
           <t xml:space="preserve">Caleb Martin out; Santi Aldama out; </t>
         </is>
       </c>
+      <c r="AE46" t="inlineStr"/>
+      <c r="AF46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6531,6 +6631,8 @@
           <t xml:space="preserve">T.J. McConnell out; Aaron Nesmith out; Johnny Furphy out; </t>
         </is>
       </c>
+      <c r="AE47" t="inlineStr"/>
+      <c r="AF47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6649,6 +6751,8 @@
           <t xml:space="preserve">Jonathan Isaac out; Anthony Black out; Noah Penda out; </t>
         </is>
       </c>
+      <c r="AE48" t="inlineStr"/>
+      <c r="AF48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6767,6 +6871,8 @@
           <t xml:space="preserve">Jusuf Nurkic out; Tony Bradley out; Trey Alexander out; </t>
         </is>
       </c>
+      <c r="AE49" t="inlineStr"/>
+      <c r="AF49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6885,6 +6991,8 @@
           <t xml:space="preserve">Jamir Watkins out; Tristan Vukcevic out; </t>
         </is>
       </c>
+      <c r="AE50" t="inlineStr"/>
+      <c r="AF50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7003,6 +7111,8 @@
           <t xml:space="preserve">Jamir Watkins out; Tristan Vukcevic out; </t>
         </is>
       </c>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7119,6 +7229,8 @@
           <t xml:space="preserve">Caleb Martin out; Santi Aldama out; </t>
         </is>
       </c>
+      <c r="AE52" t="inlineStr"/>
+      <c r="AF52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7235,6 +7347,8 @@
           <t xml:space="preserve">Nic Claxton out; Jordan Hawkins out; </t>
         </is>
       </c>
+      <c r="AE53" t="inlineStr"/>
+      <c r="AF53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7351,6 +7465,8 @@
           <t xml:space="preserve">Brandon Ingram out; Max Strus out; Jordan Miller out; Yanic Konan Niederhauser out; </t>
         </is>
       </c>
+      <c r="AE54" t="inlineStr"/>
+      <c r="AF54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7467,6 +7583,8 @@
           <t xml:space="preserve">Grant Williams out; Coby White out; Kon Knueppel out; </t>
         </is>
       </c>
+      <c r="AE55" t="inlineStr"/>
+      <c r="AF55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7585,6 +7703,8 @@
           <t xml:space="preserve">Mark Williams out; </t>
         </is>
       </c>
+      <c r="AE56" t="inlineStr"/>
+      <c r="AF56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7697,6 +7817,8 @@
         <v>0</v>
       </c>
       <c r="AD57" t="inlineStr"/>
+      <c r="AE57" t="inlineStr"/>
+      <c r="AF57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7815,6 +7937,8 @@
           <t xml:space="preserve">Mark Williams out; </t>
         </is>
       </c>
+      <c r="AE58" t="inlineStr"/>
+      <c r="AF58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7933,6 +8057,8 @@
           <t xml:space="preserve">Mouhamed Gueye out; </t>
         </is>
       </c>
+      <c r="AE59" t="inlineStr"/>
+      <c r="AF59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8049,6 +8175,8 @@
           <t xml:space="preserve">Jusuf Nurkic out; Tony Bradley out; Trey Alexander out; </t>
         </is>
       </c>
+      <c r="AE60" t="inlineStr"/>
+      <c r="AF60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8163,6 +8291,8 @@
         <v>0</v>
       </c>
       <c r="AD61" t="inlineStr"/>
+      <c r="AE61" t="inlineStr"/>
+      <c r="AF61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8277,6 +8407,8 @@
         <v>0</v>
       </c>
       <c r="AD62" t="inlineStr"/>
+      <c r="AE62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8391,6 +8523,8 @@
         <v>0</v>
       </c>
       <c r="AD63" t="inlineStr"/>
+      <c r="AE63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8505,6 +8639,8 @@
         <v>0</v>
       </c>
       <c r="AD64" t="inlineStr"/>
+      <c r="AE64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8619,6 +8755,8 @@
         <v>0</v>
       </c>
       <c r="AD65" t="inlineStr"/>
+      <c r="AE65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8737,6 +8875,8 @@
           <t xml:space="preserve">Mouhamed Gueye out; </t>
         </is>
       </c>
+      <c r="AE66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8855,6 +8995,8 @@
           <t xml:space="preserve">Branden Carlson out; Shaedon Sharpe out; </t>
         </is>
       </c>
+      <c r="AE67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8973,6 +9115,8 @@
           <t xml:space="preserve">Jimmy Butler III out; Kristaps Porzingis out; Moses Moody out; Brandin Podziemski out; </t>
         </is>
       </c>
+      <c r="AE68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9087,6 +9231,8 @@
         <v>0</v>
       </c>
       <c r="AD69" t="inlineStr"/>
+      <c r="AE69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9201,6 +9347,8 @@
         <v>0</v>
       </c>
       <c r="AD70" t="inlineStr"/>
+      <c r="AE70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9317,6 +9465,8 @@
           <t xml:space="preserve">Branden Carlson out; Shaedon Sharpe out; </t>
         </is>
       </c>
+      <c r="AE71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9435,6 +9585,8 @@
           <t xml:space="preserve">Brandon Ingram out; Max Strus out; Jordan Miller out; Yanic Konan Niederhauser out; </t>
         </is>
       </c>
+      <c r="AE72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9549,6 +9701,8 @@
         <v>0</v>
       </c>
       <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9667,6 +9821,8 @@
           <t xml:space="preserve">Caleb Martin out; Santi Aldama out; </t>
         </is>
       </c>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9781,6 +9937,8 @@
         <v>0</v>
       </c>
       <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9899,6 +10057,8 @@
           <t xml:space="preserve">Jonathan Isaac out; Anthony Black out; Noah Penda out; </t>
         </is>
       </c>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10017,6 +10177,8 @@
           <t xml:space="preserve">Jonathan Isaac out; Anthony Black out; Noah Penda out; </t>
         </is>
       </c>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10135,6 +10297,8 @@
           <t xml:space="preserve">Mark Williams out; </t>
         </is>
       </c>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10253,6 +10417,8 @@
           <t xml:space="preserve">Nic Claxton out; Jordan Hawkins out; </t>
         </is>
       </c>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10371,6 +10537,8 @@
           <t xml:space="preserve">Dylan Cardwell out; Maxime Raynaud out; </t>
         </is>
       </c>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10485,6 +10653,8 @@
         <v>0</v>
       </c>
       <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10603,6 +10773,8 @@
           <t xml:space="preserve">Caleb Martin out; Santi Aldama out; </t>
         </is>
       </c>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10719,6 +10891,8 @@
           <t xml:space="preserve">Jusuf Nurkic out; Tony Bradley out; Trey Alexander out; </t>
         </is>
       </c>
+      <c r="AE83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10837,6 +11011,8 @@
           <t xml:space="preserve">Caleb Martin out; Santi Aldama out; </t>
         </is>
       </c>
+      <c r="AE84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10955,6 +11131,8 @@
           <t xml:space="preserve">Jamir Watkins out; Tristan Vukcevic out; </t>
         </is>
       </c>
+      <c r="AE85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11071,6 +11249,8 @@
           <t xml:space="preserve">Branden Carlson out; Shaedon Sharpe out; </t>
         </is>
       </c>
+      <c r="AE86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11189,6 +11369,8 @@
           <t xml:space="preserve">Mark Williams out; </t>
         </is>
       </c>
+      <c r="AE87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11305,6 +11487,8 @@
           <t xml:space="preserve">Brandon Ingram out; Max Strus out; Jordan Miller out; Yanic Konan Niederhauser out; </t>
         </is>
       </c>
+      <c r="AE88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11423,6 +11607,8 @@
           <t xml:space="preserve">Jonathan Isaac out; Anthony Black out; Noah Penda out; </t>
         </is>
       </c>
+      <c r="AE89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11537,6 +11723,8 @@
         <v>0</v>
       </c>
       <c r="AD90" t="inlineStr"/>
+      <c r="AE90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11655,6 +11843,8 @@
           <t xml:space="preserve">Mouhamed Gueye out; </t>
         </is>
       </c>
+      <c r="AE91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11769,6 +11959,8 @@
         <v>0</v>
       </c>
       <c r="AD92" t="inlineStr"/>
+      <c r="AE92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11883,6 +12075,8 @@
         <v>0</v>
       </c>
       <c r="AD93" t="inlineStr"/>
+      <c r="AE93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -12001,6 +12195,8 @@
           <t xml:space="preserve">T.J. McConnell out; Aaron Nesmith out; Johnny Furphy out; </t>
         </is>
       </c>
+      <c r="AE94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12119,6 +12315,8 @@
           <t xml:space="preserve">Donte DiVincenzo out; </t>
         </is>
       </c>
+      <c r="AE95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -12235,6 +12433,8 @@
           <t xml:space="preserve">Brandon Ingram out; Max Strus out; Jordan Miller out; Yanic Konan Niederhauser out; </t>
         </is>
       </c>
+      <c r="AE96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12351,6 +12551,8 @@
           <t xml:space="preserve">Nic Claxton out; Jordan Hawkins out; </t>
         </is>
       </c>
+      <c r="AE97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12469,6 +12671,8 @@
           <t xml:space="preserve">Jamir Watkins out; Tristan Vukcevic out; </t>
         </is>
       </c>
+      <c r="AE98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12585,6 +12789,8 @@
           <t xml:space="preserve">Grant Williams out; Coby White out; Kon Knueppel out; </t>
         </is>
       </c>
+      <c r="AE99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12699,6 +12905,8 @@
         <v>0</v>
       </c>
       <c r="AD100" t="inlineStr"/>
+      <c r="AE100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12814,6 +13022,1242 @@
         <is>
           <t xml:space="preserve">Brandon Ingram out; Max Strus out; Jordan Miller out; Yanic Konan Niederhauser out; </t>
         </is>
+      </c>
+      <c r="AE101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NOP @ UTA</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>4066336</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lauri Markkanen</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>lauri markkanen</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>betrivers</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>-129</v>
+      </c>
+      <c r="M102" t="n">
+        <v>26.84</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.8266</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.5317</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.5802</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.0299</v>
+      </c>
+      <c r="S102" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>7469a7f48dbb77001b3148829f80c97b</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:45:33.160380+00:00</t>
+        </is>
+      </c>
+      <c r="V102" t="n">
+        <v>16</v>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X102" t="n">
+        <v>-122</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>0.5202</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>-2.41</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jusuf Nurkic out; </t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF102" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NYK @ BOS</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>3136195</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Karl-Anthony Towns</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>karl anthony towns</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>NYK</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>BOS</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>122</v>
+      </c>
+      <c r="M103" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.7107</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.4278</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.4743</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.0528</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>0d34c898f6cbb990077ae9f0a2773513</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:45:33.160380+00:00</t>
+        </is>
+      </c>
+      <c r="V103" t="n">
+        <v>3</v>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X103" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>0.0399</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>6.612399999999998</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD103" t="inlineStr"/>
+      <c r="AE103" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF103" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NOP @ UTA</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>4066336</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Lauri Markkanen</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>lauri markkanen</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>-118</v>
+      </c>
+      <c r="M104" t="n">
+        <v>36.26</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.7445000000000001</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.5122</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.5503</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>7469a7f48dbb77001b3148829f80c97b</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:45:33.160380+00:00</t>
+        </is>
+      </c>
+      <c r="V104" t="n">
+        <v>25</v>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X104" t="n">
+        <v>-118</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>0.5101</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jusuf Nurkic out; </t>
+        </is>
+      </c>
+      <c r="AE104" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF104" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>CHI @ MIL</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>5044385</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Leonard Miller</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>leonard miller</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>-109</v>
+      </c>
+      <c r="M105" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.6988</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.4898</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.5241</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.0343</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="S105" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>0cdc865f5b785c0be6bc409117fe38aa</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:45:33.160380+00:00</t>
+        </is>
+      </c>
+      <c r="V105" t="n">
+        <v>24</v>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X105" t="n">
+        <v>-109</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>-0.0005999999999999999</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>0.3119266055045872</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nic Claxton out; </t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF105" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NOP @ UTA</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>4395628</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Zion Williamson</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>zion williamson</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>-120</v>
+      </c>
+      <c r="M106" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0.7115</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.5184</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.5501</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.0317</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>7469a7f48dbb77001b3148829f80c97b</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:45:33.160380+00:00</t>
+        </is>
+      </c>
+      <c r="V106" t="n">
+        <v>30</v>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X106" t="n">
+        <v>-118</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>0.5333333333333334</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD106" t="inlineStr"/>
+      <c r="AE106" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF106" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>MEM @ GSW</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>3213</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Al Horford</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>al horford</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>GSW</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>100</v>
+      </c>
+      <c r="M107" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.6735</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.5127</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0.0316</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.0255</v>
+      </c>
+      <c r="S107" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>d7525d3e92349ef234ca0c1ac699b365</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:45:33.160380+00:00</t>
+        </is>
+      </c>
+      <c r="V107" t="n">
+        <v>8</v>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr"/>
+      <c r="Y107" t="n">
+        <v>0.4459</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>-0.0352</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jimmy Butler III out; Kristaps Porzingis out; Moses Moody out; </t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF107" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>DET @ MIA</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>4684742</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Ausar Thompson</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>ausar thompson</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>-110</v>
+      </c>
+      <c r="M108" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.7246</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.5373</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.5681</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0.0308</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0.08459999999999999</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>db951d9ee1d6777d7ced41eba05aac44</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:45:33.160380+00:00</t>
+        </is>
+      </c>
+      <c r="V108" t="n">
+        <v>4</v>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X108" t="n">
+        <v>-148</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0.0267</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>5.290909090909092</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC108" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD108" t="inlineStr"/>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF108" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NOP @ UTA</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>4397688</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Trey Murphy III</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>trey murphy</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>-107</v>
+      </c>
+      <c r="M109" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.4877</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.5182</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>7469a7f48dbb77001b3148829f80c97b</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:45:33.160380+00:00</t>
+        </is>
+      </c>
+      <c r="V109" t="n">
+        <v>18</v>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X109" t="n">
+        <v>-105</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0.4797</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD109" t="inlineStr"/>
+      <c r="AE109" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF109" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>DET @ MIA</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>3032977</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Giannis Antetokounmpo</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>giannis antetokounmpo</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>108</v>
+      </c>
+      <c r="M110" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.6254</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0.0249</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>db951d9ee1d6777d7ced41eba05aac44</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:45:33.160380+00:00</t>
+        </is>
+      </c>
+      <c r="V110" t="n">
+        <v>5</v>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X110" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0.4473</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0.9504</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="inlineStr"/>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF110" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>DET @ MIA</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>3032977</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Giannis Antetokounmpo</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>giannis antetokounmpo</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>DET</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M111" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.6497000000000001</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.5226</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.5417</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.0191</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>db951d9ee1d6777d7ced41eba05aac44</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:45:33.160380+00:00</t>
+        </is>
+      </c>
+      <c r="V111" t="n">
+        <v>12</v>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X111" t="n">
+        <v>-126</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0.5289</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="inlineStr"/>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF111" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/performance_report.xlsx
+++ b/outputs/performance_report.xlsx
@@ -474,31 +474,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="C2" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D2" t="n">
-        <v>0.464</v>
+        <v>0.46</v>
       </c>
       <c r="E2" t="n">
-        <v>1444.86</v>
+        <v>1490.09</v>
       </c>
       <c r="F2" t="n">
-        <v>-49.92</v>
+        <v>-70.29000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0346</v>
+        <v>-0.0472</v>
       </c>
       <c r="H2" t="n">
-        <v>0.542</v>
+        <v>0.539</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0009</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.455</v>
+        <v>0.427</v>
       </c>
     </row>
   </sheetData>
@@ -574,31 +574,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.588</v>
+        <v>0.579</v>
       </c>
       <c r="E2" t="n">
-        <v>223.12</v>
+        <v>226.17</v>
       </c>
       <c r="F2" t="n">
-        <v>20.7</v>
+        <v>18.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0827</v>
       </c>
       <c r="H2" t="n">
-        <v>0.51</v>
+        <v>0.511</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0059</v>
+        <v>0.0016</v>
       </c>
       <c r="J2" t="n">
-        <v>0.588</v>
+        <v>0.526</v>
       </c>
     </row>
     <row r="3">
@@ -608,31 +608,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="E3" t="n">
-        <v>85.13</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>14.82</v>
+        <v>21.03</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1741</v>
+        <v>0.2247</v>
       </c>
       <c r="H3" t="n">
-        <v>0.532</v>
+        <v>0.521</v>
       </c>
       <c r="I3" t="n">
         <v>0.0232</v>
       </c>
       <c r="J3" t="n">
-        <v>0.667</v>
+        <v>0.444</v>
       </c>
     </row>
     <row r="4">
@@ -642,22 +642,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C4" t="n">
         <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>0.42</v>
+        <v>0.404</v>
       </c>
       <c r="E4" t="n">
-        <v>664.1900000000001</v>
+        <v>674.27</v>
       </c>
       <c r="F4" t="n">
-        <v>-70.55</v>
+        <v>-80.63</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1062</v>
+        <v>-0.1196</v>
       </c>
       <c r="H4" t="n">
         <v>0.551</v>
@@ -666,7 +666,7 @@
         <v>-0.0067</v>
       </c>
       <c r="J4" t="n">
-        <v>0.34</v>
+        <v>0.327</v>
       </c>
     </row>
     <row r="5">
@@ -676,31 +676,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>0.545</v>
+        <v>0.5</v>
       </c>
       <c r="E5" t="n">
-        <v>317.62</v>
+        <v>328.92</v>
       </c>
       <c r="F5" t="n">
-        <v>12.33</v>
+        <v>1.03</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0388</v>
+        <v>0.0031</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>-0.008200000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.318</v>
+        <v>0.292</v>
       </c>
     </row>
     <row r="6">
@@ -710,31 +710,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>0.333</v>
+        <v>0.4</v>
       </c>
       <c r="E6" t="n">
-        <v>154.8</v>
+        <v>167.16</v>
       </c>
       <c r="F6" t="n">
-        <v>-27.22</v>
+        <v>-30.41</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1758</v>
+        <v>-0.1819</v>
       </c>
       <c r="H6" t="n">
-        <v>0.528</v>
+        <v>0.522</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0123</v>
+        <v>0.0163</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
@@ -810,22 +810,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C2" t="n">
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>0.444</v>
+        <v>0.438</v>
       </c>
       <c r="E2" t="n">
-        <v>947.97</v>
+        <v>949.25</v>
       </c>
       <c r="F2" t="n">
-        <v>-53.5</v>
+        <v>-54.78</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0564</v>
+        <v>-0.0577</v>
       </c>
       <c r="H2" t="n">
         <v>0.539</v>
@@ -834,7 +834,7 @@
         <v>-0.0068</v>
       </c>
       <c r="J2" t="n">
-        <v>0.347</v>
+        <v>0.342</v>
       </c>
     </row>
     <row r="3">
@@ -844,31 +844,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
       <c r="E3" t="n">
-        <v>496.89</v>
+        <v>540.84</v>
       </c>
       <c r="F3" t="n">
-        <v>3.58</v>
+        <v>-15.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0072</v>
+        <v>-0.0287</v>
       </c>
       <c r="H3" t="n">
-        <v>0.548</v>
+        <v>0.54</v>
       </c>
       <c r="I3" t="n">
-        <v>0.009900000000000001</v>
+        <v>0.0095</v>
       </c>
       <c r="J3" t="n">
-        <v>0.658</v>
+        <v>0.549</v>
       </c>
     </row>
   </sheetData>
@@ -919,16 +919,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>0.482</v>
+        <v>0.483</v>
       </c>
       <c r="D2" t="n">
-        <v>0.375</v>
+        <v>0.419</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.107</v>
+        <v>-0.064</v>
       </c>
     </row>
     <row r="3">
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C3" t="n">
-        <v>0.537</v>
+        <v>0.536</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="E3" t="n">
-        <v>0.022</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="4">
@@ -957,16 +957,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
         <v>0.5610000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>0.472</v>
+        <v>0.462</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.089</v>
+        <v>-0.099</v>
       </c>
     </row>
     <row r="5">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>0.593</v>
       </c>
       <c r="D5" t="n">
-        <v>0.286</v>
+        <v>0.267</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.307</v>
+        <v>-0.326</v>
       </c>
     </row>
     <row r="6">
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF111"/>
+  <dimension ref="A1:AF125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14260,6 +14260,1690 @@
         <v>1</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SAS @ DAL</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>5037871</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>dylan harper</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>-124</v>
+      </c>
+      <c r="M112" t="n">
+        <v>20.48</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.8651</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.5256</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0.0594</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="S112" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>efb2248ad964f84921b3e700125e404b</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V112" t="n">
+        <v>29</v>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
+      <c r="AA112" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tobias Harris out; </t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF112" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SAS @ DAL</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>5037871</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>dylan harper</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>williamhill_us</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>-124</v>
+      </c>
+      <c r="M113" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.8369</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.5237000000000001</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="S113" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>efb2248ad964f84921b3e700125e404b</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V113" t="n">
+        <v>22</v>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr"/>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr"/>
+      <c r="AA113" t="n">
+        <v>-6.98</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tobias Harris out; </t>
+        </is>
+      </c>
+      <c r="AE113" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF113" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>WAS @ CHI</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>5160992</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Alex Sarr</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>alex sarr</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>CHI</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>betrivers</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>-105</v>
+      </c>
+      <c r="M114" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.6921</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.4861</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.5222</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="S114" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>cce3cd5869541979d68f7bde648f7c20</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V114" t="n">
+        <v>15</v>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr"/>
+      <c r="AA114" t="n">
+        <v>-1.28</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jamir Watkins out; Tristan Vukcevic out; </t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF114" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>MIA @ CHA</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>3032977</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Giannis Antetokounmpo</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>giannis antetokounmpo</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>108</v>
+      </c>
+      <c r="M115" t="n">
+        <v>8.99</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.6793</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.4558</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.0178</v>
+      </c>
+      <c r="S115" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>0abd50d04d02296b33809f9458fd47e4</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V115" t="n">
+        <v>6</v>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X115" t="n">
+        <v>-120</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>0.4921</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>2.2248</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF115" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SAS @ DAL</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>5037871</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>dylan harper</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>-105</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.6834</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.5308</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.0324</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="S116" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>efb2248ad964f84921b3e700125e404b</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V116" t="n">
+        <v>5</v>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
+      <c r="AA116" t="n">
+        <v>-4.77</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tobias Harris out; </t>
+        </is>
+      </c>
+      <c r="AE116" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF116" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NOP @ DEN</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>4431767</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Christian Braun</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>christian braun</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>FG3M</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>-110</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.7108</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.5198</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.5512</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.0522</v>
+      </c>
+      <c r="S117" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>0c95f2515a34d871cd4946cbf38dd670</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V117" t="n">
+        <v>0</v>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
+      <c r="AA117" t="n">
+        <v>6.527272727272727</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cameron Johnson out; Julian Strawther out; Spencer Jones out; </t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF117" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>MIA @ CHA</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>3032977</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Giannis Antetokounmpo</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>giannis antetokounmpo</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>fanatics</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>105</v>
+      </c>
+      <c r="M118" t="n">
+        <v>5.01</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.6175</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.4674</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>0abd50d04d02296b33809f9458fd47e4</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V118" t="n">
+        <v>3</v>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="n">
+        <v>0.4085</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>-0.0589</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5354999999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF118" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>MIA @ CHA</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>4066261</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Bam Adebayo</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>bam adebayo</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>-111</v>
+      </c>
+      <c r="M119" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.6354</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.5123</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.5339</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="S119" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>0abd50d04d02296b33809f9458fd47e4</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V119" t="n">
+        <v>8</v>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X119" t="n">
+        <v>-125</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.5527</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.0404</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>1.855855855855856</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF119" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>MIA @ CHA</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>4278053</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Davion Mitchell</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>davion mitchell</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>116</v>
+      </c>
+      <c r="M120" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.5645</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.4649</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>0abd50d04d02296b33809f9458fd47e4</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V120" t="n">
+        <v>1</v>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X120" t="n">
+        <v>-120</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.4724</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.0286</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.5220000000000001</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF120" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>MIA @ CHA</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>4066261</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Bam Adebayo</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>bam adebayo</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>williamhill_us</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>-118</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.6449</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.5306</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.5506</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="S121" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>0abd50d04d02296b33809f9458fd47e4</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V121" t="n">
+        <v>4</v>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X121" t="n">
+        <v>-125</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.5188</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>-0.0118</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>-2.54</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD121" t="inlineStr"/>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF121" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>MIL @ PHI</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>3059318</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>joel embiid</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>105</v>
+      </c>
+      <c r="M122" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.5939</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.5002</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.0199</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.0254</v>
+      </c>
+      <c r="S122" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>a66da208d3609b028970dfe2b5d7973f</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V122" t="n">
+        <v>11</v>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr"/>
+      <c r="AA122" t="n">
+        <v>-3.02</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LeBron James out; Dominick Barlow out; Ariel Hukporti out; </t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF122" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>BKN @ CLE</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>5175643</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Egor Demin</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>egor demin</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>williamhill_us</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>105</v>
+      </c>
+      <c r="M123" t="n">
+        <v>10</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.6056</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.5054999999999999</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.0197</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.0363</v>
+      </c>
+      <c r="S123" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>f187c8a86c1d1676bb45b9b3a6707872</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V123" t="n">
+        <v>22</v>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr"/>
+      <c r="AA123" t="n">
+        <v>-4.32</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD123" t="inlineStr"/>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF123" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>MIL @ PHI</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3059318</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>joel embiid</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>FG3M</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.5953000000000001</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.4939</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.0177</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>a66da208d3609b028970dfe2b5d7973f</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V124" t="n">
+        <v>0</v>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr"/>
+      <c r="AA124" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LeBron James out; Dominick Barlow out; Ariel Hukporti out; </t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF124" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SAS @ DAL</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>5104157</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>victor wembanyama</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>FG3M</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J125" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>130</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.5124</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.4226</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.4383</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>efb2248ad964f84921b3e700125e404b</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>2026-10-24T12:45:39.393320+00:00</t>
+        </is>
+      </c>
+      <c r="V125" t="n">
+        <v>2</v>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr"/>
+      <c r="AA125" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tobias Harris out; </t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF125" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/performance_report.xlsx
+++ b/outputs/performance_report.xlsx
@@ -8,10 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overall" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By prop" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By side" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graded bets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By tier" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By prop" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="By side" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Graded bets" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,35 +471,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALL</t>
+          <t>ALL (excl. dropped)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="C2" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D2" t="n">
-        <v>0.46</v>
+        <v>0.466</v>
       </c>
       <c r="E2" t="n">
-        <v>1490.09</v>
+        <v>1540.34</v>
       </c>
       <c r="F2" t="n">
-        <v>-70.29000000000001</v>
+        <v>-73.39</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0472</v>
+        <v>-0.0476</v>
       </c>
       <c r="H2" t="n">
         <v>0.539</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>0.427</v>
+        <v>0.418</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dropped by re-score</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="E3" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1399</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.556</v>
       </c>
     </row>
   </sheetData>
@@ -512,13 +547,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>stat</t>
+          <t>tier_base</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -568,173 +603,131 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AST</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="D2" t="n">
-        <v>0.579</v>
+        <v>0.46</v>
       </c>
       <c r="E2" t="n">
-        <v>226.17</v>
+        <v>1425.69</v>
       </c>
       <c r="F2" t="n">
-        <v>18.7</v>
+        <v>-57.55</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0827</v>
+        <v>-0.0404</v>
       </c>
       <c r="H2" t="n">
-        <v>0.511</v>
+        <v>0.543</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0016</v>
+        <v>-0.0009</v>
       </c>
       <c r="J2" t="n">
-        <v>0.526</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FG3M</t>
+          <t>blowout</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0.556</v>
+        <v>0.308</v>
       </c>
       <c r="E3" t="n">
-        <v>93.56999999999999</v>
+        <v>50.24</v>
       </c>
       <c r="F3" t="n">
-        <v>21.03</v>
+        <v>-28.18</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2247</v>
+        <v>-0.5609</v>
       </c>
       <c r="H3" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.0232</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.444</v>
-      </c>
+        <v>0.518</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PRA</t>
+          <t>core</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.404</v>
+        <v>0.769</v>
       </c>
       <c r="E4" t="n">
-        <v>674.27</v>
+        <v>27.68</v>
       </c>
       <c r="F4" t="n">
-        <v>-80.63</v>
+        <v>19.75</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1196</v>
+        <v>0.7135</v>
       </c>
       <c r="H4" t="n">
-        <v>0.551</v>
+        <v>0.52</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0067</v>
+        <v>0.0127</v>
       </c>
       <c r="J4" t="n">
-        <v>0.327</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PTS</t>
+          <t>over (experimental)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="E5" t="n">
-        <v>328.92</v>
+        <v>36.73</v>
       </c>
       <c r="F5" t="n">
-        <v>1.03</v>
+        <v>-7.41</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0031</v>
+        <v>-0.2017</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.545</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.0003</v>
       </c>
       <c r="J5" t="n">
-        <v>0.292</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REB</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>20</v>
-      </c>
-      <c r="C6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E6" t="n">
-        <v>167.16</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-30.41</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.1819</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.0163</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -748,13 +741,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>side</t>
+          <t>stat</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -806,69 +799,171 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>over</t>
+          <t>AST</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>0.438</v>
+        <v>0.619</v>
       </c>
       <c r="E2" t="n">
-        <v>949.25</v>
+        <v>228.43</v>
       </c>
       <c r="F2" t="n">
-        <v>-54.78</v>
+        <v>21.16</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0577</v>
+        <v>0.0926</v>
       </c>
       <c r="H2" t="n">
-        <v>0.539</v>
+        <v>0.508</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0068</v>
+        <v>0.0022</v>
       </c>
       <c r="J2" t="n">
-        <v>0.342</v>
+        <v>0.524</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>under</t>
+          <t>FG3M</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>0.49</v>
+        <v>0.583</v>
       </c>
       <c r="E3" t="n">
-        <v>540.84</v>
+        <v>102.49</v>
       </c>
       <c r="F3" t="n">
-        <v>-15.5</v>
+        <v>22.5</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0287</v>
+        <v>0.2196</v>
       </c>
       <c r="H3" t="n">
-        <v>0.54</v>
+        <v>0.528</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0095</v>
+        <v>0.0168</v>
       </c>
       <c r="J3" t="n">
-        <v>0.549</v>
+        <v>0.417</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C4" t="n">
+        <v>24</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>693.8099999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-83.33</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.1201</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.551</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.333</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="E5" t="n">
+        <v>344.03</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="E6" t="n">
+        <v>171.58</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-34.83</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.203</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.727</v>
       </c>
     </row>
   </sheetData>
@@ -882,148 +977,127 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>bucket</t>
+          <t>side</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>bets</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>predicted</t>
+          <t>wins</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>actual</t>
+          <t>hit_rate</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>gap</t>
+          <t>staked</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>roi</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>avg_blended_prob</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>avg_clv</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>clv_pos_rate</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>(0.0, 0.52]</t>
+          <t>over</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="C2" t="n">
-        <v>0.483</v>
+        <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>0.419</v>
+        <v>0.442</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.064</v>
+        <v>978.33</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-56.37</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.0576</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.349</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>(0.52, 0.55]</t>
+          <t>under</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C3" t="n">
-        <v>0.536</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
-        <v>0.541</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>(0.55, 0.58]</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>39</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.5610000000000001</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.462</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.099</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>(0.58, 0.62]</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>15</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.267</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.326</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>(0.62, 0.66]</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.373</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>(0.66, 1.0]</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.661</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.339</v>
+        <v>562.01</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-17.02</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.0303</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.517</v>
       </c>
     </row>
   </sheetData>
@@ -1037,534 +1111,697 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF125"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>bucket</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>game</t>
+          <t>n</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>player_id</t>
+          <t>predicted</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>player</t>
+          <t>actual</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>player_key</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>team</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>opp</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>stat</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>side</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>line</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>book</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>projection</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>model_prob</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>mkt_fair_prob</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>blended_prob</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>edge</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>ev_per_dollar</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>stake</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>event_id</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>fetched_utc</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>actual</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>close_price</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>close_fair_prob</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>clv</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>profit</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>n_cur</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>dtd</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>inj_note</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>tier</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>abs_spread</t>
+          <t>gap</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>UTA @ MEM</t>
-        </is>
+          <t>(0.0, 0.52]</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>37</v>
       </c>
       <c r="C2" t="n">
-        <v>4066336</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Lauri Markkanen</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>lauri markkanen</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MEM</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PTS</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>betmgm</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>-115</v>
-      </c>
-      <c r="M2" t="n">
-        <v>27.98</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.8385</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.4796</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.5873</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.1077</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="S2" t="n">
-        <v>20</v>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>e6769c813dd625b622df94c14a562ce2</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>2026-10-21T16:57:09.520485+00:00</t>
-        </is>
-      </c>
-      <c r="V2" t="n">
-        <v>18</v>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="X2" t="n">
-        <v>-115</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.4767</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-0.0029</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jusuf Nurkic out; Tony Bradley out; Trey Alexander out; </t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
+        <v>0.483</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.051</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>UTA @ MEM</t>
-        </is>
+          <t>(0.52, 0.55]</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>43</v>
       </c>
       <c r="C3" t="n">
-        <v>4066336</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Lauri Markkanen</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>lauri markkanen</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>UTA</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MEM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PRA</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>over</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>betrivers</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>-117</v>
-      </c>
-      <c r="M3" t="n">
-        <v>37.52</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.8328</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.5117</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.0963</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.1277</v>
-      </c>
-      <c r="S3" t="n">
-        <v>30</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>e6769c813dd625b622df94c14a562ce2</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>2026-10-21T16:57:09.520485+00:00</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>30</v>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="X3" t="n">
-        <v>-115</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.0015</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>-30</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jusuf Nurkic out; Tony Bradley out; Trey Alexander out; </t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
+        <v>0.537</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.025</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CHA @ BKN</t>
-        </is>
+          <t>(0.55, 0.58]</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>47</v>
       </c>
       <c r="C4" t="n">
-        <v>4396971</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Naz Reid</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>naz reid</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CHA</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>BKN</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>PRA</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>under</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fanduel</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>-108</v>
-      </c>
-      <c r="M4" t="n">
-        <v>22.82</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.8068</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.5132</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.6012999999999999</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.0881</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="S4" t="n">
-        <v>20</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>47cc511bb5ce50f715e3625ce5ef77ee</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2026-10-21T16:57:09.520485+00:00</t>
-        </is>
-      </c>
-      <c r="V4" t="n">
-        <v>38</v>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>loss</t>
-        </is>
-      </c>
-      <c r="X4" t="n">
-        <v>-104</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>-0.0102</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>-20</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Grant Williams out; Coby White out; Kon Knueppel out; </t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.093</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>(0.58, 0.62]</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.241</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>(0.62, 0.66]</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.373</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>(0.66, 1.0]</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AG147"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>game</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>player</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>player_key</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>team</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>opp</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>stat</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>side</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>line</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>book</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>model_prob</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>mkt_fair_prob</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>blended_prob</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>edge</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ev_per_dollar</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>stake</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>event_id</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>fetched_utc</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>actual</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>result</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>close_price</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>close_fair_prob</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>clv</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>profit</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>n_cur</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>dtd</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>inj_note</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>abs_spread</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>UTA @ MEM</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>4066336</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Lauri Markkanen</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>lauri markkanen</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>-115</v>
+      </c>
+      <c r="M2" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.8385</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.4796</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.5873</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.1077</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="S2" t="n">
+        <v>20</v>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>e6769c813dd625b622df94c14a562ce2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-10-21T16:57:09.520485+00:00</t>
+        </is>
+      </c>
+      <c r="V2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-115</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.0029</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jusuf Nurkic out; Tony Bradley out; Trey Alexander out; </t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UTA @ MEM</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>4066336</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lauri Markkanen</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>lauri markkanen</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>MEM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>betrivers</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M3" t="n">
+        <v>37.52</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8328</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.0963</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="S3" t="n">
+        <v>30</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>e6769c813dd625b622df94c14a562ce2</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-10-21T16:57:09.520485+00:00</t>
+        </is>
+      </c>
+      <c r="V3" t="n">
+        <v>30</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-115</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.0015</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jusuf Nurkic out; Tony Bradley out; Trey Alexander out; </t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CHA @ BKN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>4396971</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Naz Reid</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>naz reid</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CHA</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>BKN</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.8068</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.6012999999999999</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.0881</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>47cc511bb5ce50f715e3625ce5ef77ee</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-10-21T16:57:09.520485+00:00</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>38</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-104</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>-0.0102</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grant Williams out; Coby White out; Kon Knueppel out; </t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>2026-10-21</t>
         </is>
       </c>
@@ -1679,6 +1916,7 @@
       </c>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1797,6 +2035,7 @@
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1917,6 +2156,7 @@
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2035,6 +2275,7 @@
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2151,6 +2392,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2265,6 +2507,7 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2385,6 +2628,7 @@
       </c>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2501,6 +2745,7 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2615,6 +2860,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2733,6 +2979,7 @@
       </c>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2851,6 +3098,7 @@
       </c>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2971,6 +3219,7 @@
       </c>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3091,6 +3340,7 @@
       </c>
       <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3211,6 +3461,7 @@
       </c>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3331,6 +3582,7 @@
       </c>
       <c r="AE19" t="inlineStr"/>
       <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3445,6 +3697,7 @@
       </c>
       <c r="AE20" t="inlineStr"/>
       <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3565,6 +3818,7 @@
       </c>
       <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3685,6 +3939,7 @@
       </c>
       <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3801,6 +4056,7 @@
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3917,6 +4173,7 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr"/>
       <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4033,6 +4290,7 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4151,6 +4409,7 @@
       </c>
       <c r="AE26" t="inlineStr"/>
       <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4271,6 +4530,7 @@
       </c>
       <c r="AE27" t="inlineStr"/>
       <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4391,6 +4651,7 @@
       </c>
       <c r="AE28" t="inlineStr"/>
       <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4509,6 +4770,7 @@
       </c>
       <c r="AE29" t="inlineStr"/>
       <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4625,6 +4887,7 @@
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4745,6 +5008,7 @@
       </c>
       <c r="AE31" t="inlineStr"/>
       <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4863,6 +5127,7 @@
       </c>
       <c r="AE32" t="inlineStr"/>
       <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4983,6 +5248,7 @@
       </c>
       <c r="AE33" t="inlineStr"/>
       <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5103,6 +5369,7 @@
       </c>
       <c r="AE34" t="inlineStr"/>
       <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5221,6 +5488,7 @@
       </c>
       <c r="AE35" t="inlineStr"/>
       <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5335,6 +5603,7 @@
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr"/>
       <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5449,6 +5718,7 @@
       </c>
       <c r="AE37" t="inlineStr"/>
       <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5563,6 +5833,7 @@
       <c r="AD38" t="inlineStr"/>
       <c r="AE38" t="inlineStr"/>
       <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5683,6 +5954,7 @@
       </c>
       <c r="AE39" t="inlineStr"/>
       <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5799,6 +6071,7 @@
       <c r="AD40" t="inlineStr"/>
       <c r="AE40" t="inlineStr"/>
       <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5919,6 +6192,7 @@
       </c>
       <c r="AE41" t="inlineStr"/>
       <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6039,6 +6313,7 @@
       </c>
       <c r="AE42" t="inlineStr"/>
       <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6155,6 +6430,7 @@
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr"/>
       <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6275,6 +6551,7 @@
       </c>
       <c r="AE44" t="inlineStr"/>
       <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6395,6 +6672,7 @@
       </c>
       <c r="AE45" t="inlineStr"/>
       <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6513,6 +6791,7 @@
       </c>
       <c r="AE46" t="inlineStr"/>
       <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6633,6 +6912,7 @@
       </c>
       <c r="AE47" t="inlineStr"/>
       <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6753,6 +7033,7 @@
       </c>
       <c r="AE48" t="inlineStr"/>
       <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6873,6 +7154,7 @@
       </c>
       <c r="AE49" t="inlineStr"/>
       <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6993,6 +7275,7 @@
       </c>
       <c r="AE50" t="inlineStr"/>
       <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7113,6 +7396,7 @@
       </c>
       <c r="AE51" t="inlineStr"/>
       <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7231,6 +7515,7 @@
       </c>
       <c r="AE52" t="inlineStr"/>
       <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7349,6 +7634,7 @@
       </c>
       <c r="AE53" t="inlineStr"/>
       <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7467,6 +7753,7 @@
       </c>
       <c r="AE54" t="inlineStr"/>
       <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7585,6 +7872,7 @@
       </c>
       <c r="AE55" t="inlineStr"/>
       <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7705,6 +7993,7 @@
       </c>
       <c r="AE56" t="inlineStr"/>
       <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7819,6 +8108,7 @@
       <c r="AD57" t="inlineStr"/>
       <c r="AE57" t="inlineStr"/>
       <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7939,6 +8229,7 @@
       </c>
       <c r="AE58" t="inlineStr"/>
       <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8059,6 +8350,7 @@
       </c>
       <c r="AE59" t="inlineStr"/>
       <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8177,6 +8469,7 @@
       </c>
       <c r="AE60" t="inlineStr"/>
       <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8293,6 +8586,7 @@
       <c r="AD61" t="inlineStr"/>
       <c r="AE61" t="inlineStr"/>
       <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8409,6 +8703,7 @@
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr"/>
       <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8525,6 +8820,7 @@
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
       <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8641,6 +8937,7 @@
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="inlineStr"/>
       <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8757,6 +9054,7 @@
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="inlineStr"/>
       <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8877,6 +9175,7 @@
       </c>
       <c r="AE66" t="inlineStr"/>
       <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8997,6 +9296,7 @@
       </c>
       <c r="AE67" t="inlineStr"/>
       <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9117,6 +9417,7 @@
       </c>
       <c r="AE68" t="inlineStr"/>
       <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9233,6 +9534,7 @@
       <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="inlineStr"/>
       <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9349,6 +9651,7 @@
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="inlineStr"/>
       <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9467,6 +9770,7 @@
       </c>
       <c r="AE71" t="inlineStr"/>
       <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9587,6 +9891,7 @@
       </c>
       <c r="AE72" t="inlineStr"/>
       <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9703,6 +10008,7 @@
       <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="inlineStr"/>
       <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9823,6 +10129,7 @@
       </c>
       <c r="AE74" t="inlineStr"/>
       <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9939,6 +10246,7 @@
       <c r="AD75" t="inlineStr"/>
       <c r="AE75" t="inlineStr"/>
       <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -10059,6 +10367,7 @@
       </c>
       <c r="AE76" t="inlineStr"/>
       <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -10179,6 +10488,7 @@
       </c>
       <c r="AE77" t="inlineStr"/>
       <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10299,6 +10609,7 @@
       </c>
       <c r="AE78" t="inlineStr"/>
       <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10419,6 +10730,7 @@
       </c>
       <c r="AE79" t="inlineStr"/>
       <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10539,6 +10851,7 @@
       </c>
       <c r="AE80" t="inlineStr"/>
       <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10655,6 +10968,7 @@
       <c r="AD81" t="inlineStr"/>
       <c r="AE81" t="inlineStr"/>
       <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10775,6 +11089,7 @@
       </c>
       <c r="AE82" t="inlineStr"/>
       <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10893,6 +11208,7 @@
       </c>
       <c r="AE83" t="inlineStr"/>
       <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -11013,6 +11329,7 @@
       </c>
       <c r="AE84" t="inlineStr"/>
       <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -11133,6 +11450,7 @@
       </c>
       <c r="AE85" t="inlineStr"/>
       <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -11251,6 +11569,7 @@
       </c>
       <c r="AE86" t="inlineStr"/>
       <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11371,6 +11690,7 @@
       </c>
       <c r="AE87" t="inlineStr"/>
       <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11489,6 +11809,7 @@
       </c>
       <c r="AE88" t="inlineStr"/>
       <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11609,6 +11930,7 @@
       </c>
       <c r="AE89" t="inlineStr"/>
       <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11725,6 +12047,7 @@
       <c r="AD90" t="inlineStr"/>
       <c r="AE90" t="inlineStr"/>
       <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11845,6 +12168,7 @@
       </c>
       <c r="AE91" t="inlineStr"/>
       <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11961,6 +12285,7 @@
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr"/>
       <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -12077,6 +12402,7 @@
       <c r="AD93" t="inlineStr"/>
       <c r="AE93" t="inlineStr"/>
       <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -12197,6 +12523,7 @@
       </c>
       <c r="AE94" t="inlineStr"/>
       <c r="AF94" t="inlineStr"/>
+      <c r="AG94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -12317,6 +12644,7 @@
       </c>
       <c r="AE95" t="inlineStr"/>
       <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -12435,6 +12763,7 @@
       </c>
       <c r="AE96" t="inlineStr"/>
       <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12553,6 +12882,7 @@
       </c>
       <c r="AE97" t="inlineStr"/>
       <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12673,6 +13003,7 @@
       </c>
       <c r="AE98" t="inlineStr"/>
       <c r="AF98" t="inlineStr"/>
+      <c r="AG98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12791,6 +13122,7 @@
       </c>
       <c r="AE99" t="inlineStr"/>
       <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12907,6 +13239,7 @@
       <c r="AD100" t="inlineStr"/>
       <c r="AE100" t="inlineStr"/>
       <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -13025,6 +13358,7 @@
       </c>
       <c r="AE101" t="inlineStr"/>
       <c r="AF101" t="inlineStr"/>
+      <c r="AG101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -13151,6 +13485,7 @@
       <c r="AF102" t="n">
         <v>2</v>
       </c>
+      <c r="AG102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -13273,6 +13608,7 @@
       <c r="AF103" t="n">
         <v>2.5</v>
       </c>
+      <c r="AG103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -13399,6 +13735,7 @@
       <c r="AF104" t="n">
         <v>2</v>
       </c>
+      <c r="AG104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -13525,6 +13862,7 @@
       <c r="AF105" t="n">
         <v>1</v>
       </c>
+      <c r="AG105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13647,6 +13985,7 @@
       <c r="AF106" t="n">
         <v>2</v>
       </c>
+      <c r="AG106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13771,6 +14110,7 @@
       <c r="AF107" t="n">
         <v>3</v>
       </c>
+      <c r="AG107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13893,6 +14233,7 @@
       <c r="AF108" t="n">
         <v>1</v>
       </c>
+      <c r="AG108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -14015,6 +14356,7 @@
       <c r="AF109" t="n">
         <v>2</v>
       </c>
+      <c r="AG109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -14137,6 +14479,7 @@
       <c r="AF110" t="n">
         <v>1</v>
       </c>
+      <c r="AG110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -14259,6 +14602,7 @@
       <c r="AF111" t="n">
         <v>1</v>
       </c>
+      <c r="AG111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -14379,6 +14723,7 @@
       <c r="AF112" t="n">
         <v>12.5</v>
       </c>
+      <c r="AG112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -14499,6 +14844,7 @@
       <c r="AF113" t="n">
         <v>12.5</v>
       </c>
+      <c r="AG113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -14619,6 +14965,7 @@
       <c r="AF114" t="n">
         <v>1.5</v>
       </c>
+      <c r="AG114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -14741,6 +15088,7 @@
       <c r="AF115" t="n">
         <v>3.5</v>
       </c>
+      <c r="AG115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14861,6 +15209,7 @@
       <c r="AF116" t="n">
         <v>12.5</v>
       </c>
+      <c r="AG116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14981,6 +15330,7 @@
       <c r="AF117" t="n">
         <v>11.5</v>
       </c>
+      <c r="AG117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -15101,6 +15451,7 @@
       <c r="AF118" t="n">
         <v>3.5</v>
       </c>
+      <c r="AG118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -15223,6 +15574,7 @@
       <c r="AF119" t="n">
         <v>3.5</v>
       </c>
+      <c r="AG119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -15345,6 +15697,7 @@
       <c r="AF120" t="n">
         <v>3.5</v>
       </c>
+      <c r="AG120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -15467,6 +15820,7 @@
       <c r="AF121" t="n">
         <v>3.5</v>
       </c>
+      <c r="AG121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -15587,6 +15941,7 @@
       <c r="AF122" t="n">
         <v>12.5</v>
       </c>
+      <c r="AG122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -15703,6 +16058,7 @@
       <c r="AF123" t="n">
         <v>11</v>
       </c>
+      <c r="AG123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -15823,6 +16179,7 @@
       <c r="AF124" t="n">
         <v>12.5</v>
       </c>
+      <c r="AG124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15943,6 +16300,2729 @@
       <c r="AF125" t="n">
         <v>12.5</v>
       </c>
+      <c r="AG125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>OKC @ DAL</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>4900671</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Ajay Mitchell</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>ajay mitchell</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>betrivers</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M126" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.5076000000000001</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.5666</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.0912</v>
+      </c>
+      <c r="S126" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>1e3ca91e27ded6e4b4bb35aabb67b505</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V126" t="n">
+        <v>36</v>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr"/>
+      <c r="AA126" t="n">
+        <v>2.851851851851852</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC126" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alex Caruso out; Chet Holmgren out; Jalen Williams out; Cason Wallace out; Nikola Topic out; </t>
+        </is>
+      </c>
+      <c r="AE126" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF126" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>OKC @ DAL</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>4278073</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>shai gilgeous alexander</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J127" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>-123</v>
+      </c>
+      <c r="M127" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.7943</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.5183</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.0524</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="S127" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>1e3ca91e27ded6e4b4bb35aabb67b505</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V127" t="n">
+        <v>29</v>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr"/>
+      <c r="Z127" t="inlineStr"/>
+      <c r="AA127" t="n">
+        <v>-2.67</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alex Caruso out; Chet Holmgren out; Jalen Williams out; Cason Wallace out; Nikola Topic out; </t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF127" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>PHI @ IND</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>3059318</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>joel embiid</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M128" t="n">
+        <v>27.54</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.5189</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.5677</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.0488</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="S128" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>5997ee5c9fbdc53f9c86732b02f58158</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V128" t="n">
+        <v>21</v>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="n">
+        <v>0.5752</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.0563</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dominick Barlow out; Ariel Hukporti out; </t>
+        </is>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF128" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>OKC @ DAL</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>4278073</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Shai Gilgeous-Alexander</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>shai gilgeous alexander</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M129" t="n">
+        <v>36.64</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.7719</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.5189</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.0481</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="S129" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>1e3ca91e27ded6e4b4bb35aabb67b505</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V129" t="n">
+        <v>21</v>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
+      <c r="AA129" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alex Caruso out; Chet Holmgren out; Jalen Williams out; Cason Wallace out; Nikola Topic out; </t>
+        </is>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF129" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>DEN @ NOP</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>4397688</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Trey Murphy III</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>trey murphy</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>fanatics</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>-115</v>
+      </c>
+      <c r="M130" t="n">
+        <v>30.88</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.7533</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.0446</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.0373</v>
+      </c>
+      <c r="S130" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>782d6ce7f65b592ad1c43d2f4e53cc82</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V130" t="n">
+        <v>10</v>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr"/>
+      <c r="Y130" t="n">
+        <v>0.5306</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>-2.68</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yves Missi out; </t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF130" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SAS @ UTA</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>5037871</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>dylan harper</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M131" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.7216</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.5421</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.0421</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.0219</v>
+      </c>
+      <c r="S131" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>e74d54621abaed183e569394f935c362</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V131" t="n">
+        <v>26</v>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr"/>
+      <c r="AA131" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tobias Harris out; </t>
+        </is>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF131" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>PHI @ IND</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>4431678</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>tyrese maxey</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M132" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.6942</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.4899</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.5286999999999999</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="S132" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>5997ee5c9fbdc53f9c86732b02f58158</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V132" t="n">
+        <v>36</v>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr"/>
+      <c r="Y132" t="n">
+        <v>0.4858</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>-0.0041</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>2.317307692307693</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dominick Barlow out; Ariel Hukporti out; </t>
+        </is>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF132" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SAS @ UTA</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>5037871</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>dylan harper</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J133" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>115</v>
+      </c>
+      <c r="M133" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.6425</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.4829</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.0374</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.0383</v>
+      </c>
+      <c r="S133" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>e74d54621abaed183e569394f935c362</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V133" t="n">
+        <v>5</v>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr"/>
+      <c r="Y133" t="inlineStr"/>
+      <c r="Z133" t="inlineStr"/>
+      <c r="AA133" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tobias Harris out; </t>
+        </is>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF133" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>PHI @ IND</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>4431678</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Tyrese Maxey</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>tyrese maxey</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>102</v>
+      </c>
+      <c r="M134" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.6709000000000001</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.5179</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.0359</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.0461</v>
+      </c>
+      <c r="S134" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>5997ee5c9fbdc53f9c86732b02f58158</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V134" t="n">
+        <v>27</v>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X134" t="n">
+        <v>104</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.4628</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>2.8764</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dominick Barlow out; Ariel Hukporti out; </t>
+        </is>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF134" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>DEN @ NOP</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>4395628</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Zion Williamson</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>zion williamson</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M135" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.5203</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.5561</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.0358</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.0314</v>
+      </c>
+      <c r="S135" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>782d6ce7f65b592ad1c43d2f4e53cc82</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V135" t="n">
+        <v>25</v>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X135" t="n">
+        <v>-110</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.0203</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>1.965811965811966</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yves Missi out; </t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF135" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>DEN @ NOP</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>4397688</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Trey Murphy III</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>trey murphy</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>DEN</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J136" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>fanduel</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>-114</v>
+      </c>
+      <c r="M136" t="n">
+        <v>21.35</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.7068</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.5138</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.5492</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.0354</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="S136" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>782d6ce7f65b592ad1c43d2f4e53cc82</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V136" t="n">
+        <v>6</v>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr"/>
+      <c r="Y136" t="n">
+        <v>0.5255</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yves Missi out; </t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF136" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SAS @ UTA</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>4395630</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Devin Vassell</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>devin vassell</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>100</v>
+      </c>
+      <c r="M137" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.5058</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.0348</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.0116</v>
+      </c>
+      <c r="S137" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>e74d54621abaed183e569394f935c362</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V137" t="n">
+        <v>2</v>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr"/>
+      <c r="Y137" t="inlineStr"/>
+      <c r="Z137" t="inlineStr"/>
+      <c r="AA137" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tobias Harris out; </t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF137" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>PHI @ IND</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>3059318</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Joel Embiid</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>joel embiid</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>betrivers</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>-118</v>
+      </c>
+      <c r="M138" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.6992</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.5101</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.5448</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.0347</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>5997ee5c9fbdc53f9c86732b02f58158</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V138" t="n">
+        <v>34</v>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X138" t="n">
+        <v>-122</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.5253</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dominick Barlow out; Ariel Hukporti out; </t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF138" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>OKC @ DAL</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>4900671</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Ajay Mitchell</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>ajay mitchell</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>OKC</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>DAL</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M139" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.6721</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.5247000000000001</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.0106</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>1e3ca91e27ded6e4b4bb35aabb67b505</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V139" t="n">
+        <v>29</v>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr"/>
+      <c r="Y139" t="inlineStr"/>
+      <c r="Z139" t="inlineStr"/>
+      <c r="AA139" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC139" t="b">
+        <v>1</v>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alex Caruso out; Chet Holmgren out; Jalen Williams out; Cason Wallace out; Nikola Topic out; </t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF139" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SAS @ UTA</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>5037871</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Dylan Harper</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>dylan harper</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>PTS</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M140" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.7030999999999999</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.5246</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.5585</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="S140" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>e74d54621abaed183e569394f935c362</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V140" t="n">
+        <v>13</v>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr"/>
+      <c r="Y140" t="inlineStr"/>
+      <c r="Z140" t="inlineStr"/>
+      <c r="AA140" t="n">
+        <v>2.040983606557377</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tobias Harris out; </t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF140" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>MIA @ ATL</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>4278039</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Nickeil Alexander-Walker</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>nickeil alexander walker</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J141" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>betrivers</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M141" t="n">
+        <v>29.46</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.6871</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.5242</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.5552</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.0309</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.0465</v>
+      </c>
+      <c r="S141" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>cc7f8bc2a4554b89f2a35abad3a633ef</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V141" t="n">
+        <v>27</v>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr"/>
+      <c r="Y141" t="n">
+        <v>0.5409</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>2.902654867256637</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mouhamed Gueye out; </t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF141" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>HOU @ MIL</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>3134907</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Kyle Kuzma</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>kyle kuzma</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>REB</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>-103</v>
+      </c>
+      <c r="M142" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.6296</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.5084</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.0284</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.0021</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>83ca338f605b5664b7b1da34c19a0222</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V142" t="n">
+        <v>6</v>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X142" t="n">
+        <v>-139</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.5407999999999999</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.0608</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF142" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>HOU @ MIL</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>3134907</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Kyle Kuzma</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>kyle kuzma</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>FG3M</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J143" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.7008</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.6135</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="S143" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>83ca338f605b5664b7b1da34c19a0222</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X143" t="n">
+        <v>-175</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.5996</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>2.813333333333333</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF143" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>HOU @ MIL</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>3134907</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Kyle Kuzma</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>kyle kuzma</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>AST</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J144" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>125</v>
+      </c>
+      <c r="M144" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="N144" t="n">
+        <v>0.5326</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="P144" t="n">
+        <v>0.4481</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.008200000000000001</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>83ca338f605b5664b7b1da34c19a0222</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V144" t="n">
+        <v>1</v>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X144" t="n">
+        <v>110</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0.4415</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF144" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SAS @ UTA</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>5104157</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Victor Wembanyama</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>victor wembanyama</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>SAS</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>UTA</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>FG3M</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J145" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>draftkings</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>133</v>
+      </c>
+      <c r="M145" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="N145" t="n">
+        <v>0.5219</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="P145" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.0292</v>
+      </c>
+      <c r="S145" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>e74d54621abaed183e569394f935c362</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V145" t="n">
+        <v>4</v>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr"/>
+      <c r="Y145" t="inlineStr"/>
+      <c r="Z145" t="inlineStr"/>
+      <c r="AA145" t="n">
+        <v>-2.74</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tobias Harris out; </t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>blowout (early)</t>
+        </is>
+      </c>
+      <c r="AF145" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>PHI @ IND</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>5124612</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>VJ Edgecombe</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>vj edgecombe</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>IND</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>PRA</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>over</t>
+        </is>
+      </c>
+      <c r="J146" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>betrivers</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>-110</v>
+      </c>
+      <c r="M146" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="N146" t="n">
+        <v>0.7000999999999999</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P146" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="S146" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>5997ee5c9fbdc53f9c86732b02f58158</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V146" t="n">
+        <v>17</v>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="X146" t="n">
+        <v>-113</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dominick Barlow out; Ariel Hukporti out; </t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>over (experimental) (early)</t>
+        </is>
+      </c>
+      <c r="AF146" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>added 22:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>WAS @ CLE</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>4576087</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Peyton Watson</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>peyton watson</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>WAS</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>FG3M</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>under</t>
+        </is>
+      </c>
+      <c r="J147" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>betmgm</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>-140</v>
+      </c>
+      <c r="M147" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N147" t="n">
+        <v>0.6766</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0.5745</v>
+      </c>
+      <c r="P147" t="n">
+        <v>0.5899</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>0.0153</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0.0112</v>
+      </c>
+      <c r="S147" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>f2a1271ffcfd7c85f51640ebff3b7ddd</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:14:04.936662+00:00</t>
+        </is>
+      </c>
+      <c r="V147" t="n">
+        <v>1</v>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="X147" t="n">
+        <v>-155</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0.5636</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>core (early)</t>
+        </is>
+      </c>
+      <c r="AF147" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>added 22:07</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
